--- a/MAJSushiConfig/ig/StructureDefinition-FRLMInformant.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMInformant.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMInformant</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMInformant</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,7 +260,7 @@
     <t>FRLMInformant.informant[x].informantProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHealthProfessional
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional
 </t>
   </si>
   <si>
@@ -270,7 +270,7 @@
     <t>FRLMInformant.informant[x].informantOrganisation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisation
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisation
 </t>
   </si>
   <si>
@@ -280,8 +280,8 @@
     <t>FRLMInformant.informant[x].informantPersonne[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMRelatedPerson
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPatient</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMRelatedPerson
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatient</t>
   </si>
   <si>
     <t>L'informateur est un patient/usager ou un autre type d'informateur (ex : aidant, personne à prévenir en cas d'urgence, etc.)</t>
@@ -599,7 +599,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.1015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.40625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/MAJSushiConfig/ig/StructureDefinition-FRLMInformant.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMInformant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
